--- a/Result/profitability/9943.xlsx
+++ b/Result/profitability/9943.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.59</v>
       </c>
       <c r="M2" t="n">
-        <v>1.39125</v>
+        <v>1.3125</v>
       </c>
       <c r="N2" t="n">
-        <v>51.565</v>
+        <v>51.3</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2975</v>
+        <v>1.14875</v>
       </c>
       <c r="N3" t="n">
-        <v>53.005</v>
+        <v>52.68</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.19</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0825</v>
+        <v>0.92875</v>
       </c>
       <c r="N4" t="n">
-        <v>53.3525</v>
+        <v>52.91</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.46</v>
       </c>
       <c r="M5" t="n">
-        <v>0.89625</v>
+        <v>0.9899999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>53.67375000000001</v>
+        <v>53.7475</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>1.23</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05375</v>
+        <v>1.0025</v>
       </c>
       <c r="N6" t="n">
-        <v>55.2775</v>
+        <v>55.45125000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9525</v>
+        <v>0.74875</v>
       </c>
       <c r="N7" t="n">
-        <v>56.32625000000001</v>
+        <v>55.49000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.46</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7162499999999999</v>
+        <v>0.57125</v>
       </c>
       <c r="N8" t="n">
-        <v>56.41500000000001</v>
+        <v>55.78375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>0.12</v>
       </c>
       <c r="M11" t="n">
-        <v>0.46875</v>
+        <v>0.4687500000000001</v>
       </c>
       <c r="N11" t="n">
         <v>55.5025</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9943</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>543</v>
+      </c>
+      <c r="D75" t="n">
+        <v>281</v>
+      </c>
+      <c r="E75" t="n">
+        <v>261</v>
+      </c>
+      <c r="F75" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="G75" t="n">
+        <v>53</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>20</v>
+      </c>
+      <c r="J75" t="n">
+        <v>73</v>
+      </c>
+      <c r="K75" t="n">
+        <v>61</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.4075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>50.4325</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6170212765957447</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.049999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09487131316926545</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.5899999999999963</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.01239756251313295</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
